--- a/data/trans_dic/P57_AF_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,59; 82,12</t>
+          <t>72,29; 82,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,8; 71,27</t>
+          <t>59,62; 70,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,57; 71,23</t>
+          <t>60,28; 72,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,56; 52,18</t>
+          <t>38,25; 52,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,1; 89,89</t>
+          <t>81,53; 89,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,86; 81,56</t>
+          <t>70,63; 81,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,03; 77,48</t>
+          <t>66,74; 77,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,36; 58,17</t>
+          <t>47,51; 57,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,31; 84,71</t>
+          <t>78,34; 84,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,98; 75,23</t>
+          <t>66,78; 74,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,28; 73,03</t>
+          <t>64,99; 73,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,0; 53,49</t>
+          <t>44,51; 53,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,12; 64,2</t>
+          <t>54,98; 64,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 55,34</t>
+          <t>46,09; 55,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,14; 83,95</t>
+          <t>76,88; 84,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,64; 60,71</t>
+          <t>49,58; 61,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,89; 67,13</t>
+          <t>58,79; 67,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,05; 55,97</t>
+          <t>47,16; 56,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,35; 84,24</t>
+          <t>77,44; 84,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,89; 56,77</t>
+          <t>48,98; 57,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,45; 64,53</t>
+          <t>58,18; 64,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,82; 54,07</t>
+          <t>47,62; 54,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,38; 83,37</t>
+          <t>78,34; 83,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,27; 57,4</t>
+          <t>50,78; 57,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,67; 52,37</t>
+          <t>41,04; 52,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,75; 63,9</t>
+          <t>52,88; 64,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,72; 77,16</t>
+          <t>67,58; 77,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,95; 45,6</t>
+          <t>33,68; 45,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,71; 46,63</t>
+          <t>35,62; 46,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,58; 72,28</t>
+          <t>61,73; 71,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,92; 79,95</t>
+          <t>71,55; 80,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,88; 52,64</t>
+          <t>42,6; 51,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,97; 47,72</t>
+          <t>40,12; 47,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,82; 66,6</t>
+          <t>59,01; 66,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,93; 77,57</t>
+          <t>70,79; 77,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 47,44</t>
+          <t>40,12; 47,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,08; 69,13</t>
+          <t>58,99; 69,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,32; 51,44</t>
+          <t>40,81; 52,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,11; 41,51</t>
+          <t>30,98; 40,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 30,79</t>
+          <t>19,54; 30,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,64; 66,76</t>
+          <t>56,71; 66,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,15; 60,51</t>
+          <t>50,45; 60,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 44,26</t>
+          <t>34,05; 44,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 30,02</t>
+          <t>14,37; 30,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,36; 66,29</t>
+          <t>59,17; 66,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,14; 54,87</t>
+          <t>47,26; 54,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,76; 40,91</t>
+          <t>33,73; 41,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 28,56</t>
+          <t>18,23; 28,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,49; 75,1</t>
+          <t>61,55; 75,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,95; 59,89</t>
+          <t>46,13; 59,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,39; 89,58</t>
+          <t>79,35; 89,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,87; 94,68</t>
+          <t>86,63; 95,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,19; 79,5</t>
+          <t>68,31; 80,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,28; 73,16</t>
+          <t>60,54; 72,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,76; 90,03</t>
+          <t>80,62; 90,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,73; 93,77</t>
+          <t>87,84; 93,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,47; 75,73</t>
+          <t>66,49; 75,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,67; 65,27</t>
+          <t>54,83; 64,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81,57; 88,7</t>
+          <t>81,12; 88,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,22; 93,46</t>
+          <t>88,34; 93,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52,81; 64,76</t>
+          <t>52,93; 64,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,44; 64,93</t>
+          <t>52,7; 65,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,0; 78,04</t>
+          <t>66,93; 77,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,74; 40,75</t>
+          <t>31,39; 41,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,83; 61,28</t>
+          <t>49,43; 61,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,58; 73,72</t>
+          <t>61,32; 72,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,57; 82,12</t>
+          <t>71,39; 82,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,3; 41,41</t>
+          <t>32,56; 41,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,52; 61,02</t>
+          <t>52,93; 61,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58,73; 67,47</t>
+          <t>59,16; 67,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70,61; 78,25</t>
+          <t>70,93; 78,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,77; 39,54</t>
+          <t>32,98; 39,83</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,19; 47,01</t>
+          <t>39,06; 47,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,48; 59,31</t>
+          <t>51,48; 59,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,43; 82,2</t>
+          <t>75,49; 82,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,61; 59,8</t>
+          <t>50,22; 60,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,03; 39,6</t>
+          <t>31,82; 39,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,85; 64,66</t>
+          <t>57,23; 65,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,2; 80,03</t>
+          <t>73,19; 80,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,83; 83,51</t>
+          <t>50,9; 80,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,88; 42,33</t>
+          <t>36,79; 42,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55,39; 60,98</t>
+          <t>55,61; 60,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75,42; 80,03</t>
+          <t>75,52; 80,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,54; 74,38</t>
+          <t>52,85; 76,22</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>69,43; 76,01</t>
+          <t>69,06; 75,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,12; 88,51</t>
+          <t>83,23; 88,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,24</t>
+          <t>81,56; 87,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,06; 81,84</t>
+          <t>27,91; 82,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,37; 82,21</t>
+          <t>76,67; 82,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,33; 85,97</t>
+          <t>80,23; 85,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,25</t>
+          <t>85,46; 90,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,87; 86,75</t>
+          <t>81,9; 86,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,03; 78,51</t>
+          <t>74,03; 78,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82,62; 86,37</t>
+          <t>82,61; 86,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84,42; 88,03</t>
+          <t>84,42; 88,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,86; 83,45</t>
+          <t>39,34; 83,39</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,15; 62,57</t>
+          <t>59,03; 62,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60,1; 63,56</t>
+          <t>60,17; 63,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,31; 75,45</t>
+          <t>72,4; 75,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39,25; 56,51</t>
+          <t>40,43; 56,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,51; 62,8</t>
+          <t>59,65; 62,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,2; 68,51</t>
+          <t>65,13; 68,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,56; 77,49</t>
+          <t>74,67; 77,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54,62; 65,2</t>
+          <t>54,5; 65,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,81; 62,09</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63,27; 65,54</t>
+          <t>63,26; 65,65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74,01; 76,13</t>
+          <t>73,99; 76,09</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,44; 58,84</t>
+          <t>49,44; 59,25</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>197571; 223501</t>
+          <t>196758; 223742</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>171162; 203993</t>
+          <t>170635; 203100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173749; 207762</t>
+          <t>175822; 210819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118602; 160507</t>
+          <t>117647; 160851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>211544; 234458</t>
+          <t>212656; 234640</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>197222; 227016</t>
+          <t>196586; 226155</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>190569; 220267</t>
+          <t>189733; 220144</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>139011; 167222</t>
+          <t>136558; 165140</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>417399; 451513</t>
+          <t>417579; 452028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>378132; 424734</t>
+          <t>377017; 422485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>375982; 420641</t>
+          <t>374347; 421259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>267777; 318288</t>
+          <t>264855; 319248</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>270238; 314713</t>
+          <t>269548; 314333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231926; 279216</t>
+          <t>232531; 279412</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>386170; 420219</t>
+          <t>384826; 421599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>257332; 314737</t>
+          <t>257004; 317112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>296767; 338285</t>
+          <t>296294; 338291</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>246436; 293174</t>
+          <t>246994; 294793</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>403129; 439021</t>
+          <t>403578; 440270</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>250666; 291021</t>
+          <t>251089; 293993</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>581143; 641580</t>
+          <t>578432; 639329</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>491765; 555996</t>
+          <t>489685; 560199</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>800885; 851778</t>
+          <t>800405; 850278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>518263; 591866</t>
+          <t>523580; 595899</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>129663; 166977</t>
+          <t>130855; 167115</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170920; 207074</t>
+          <t>171345; 207937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214428; 244335</t>
+          <t>213989; 244559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106091; 138428</t>
+          <t>102242; 137501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119761; 156411</t>
+          <t>119477; 156127</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>208643; 244917</t>
+          <t>209180; 242235</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>237899; 268172</t>
+          <t>240011; 271391</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142849; 175393</t>
+          <t>141934; 172967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>261496; 312216</t>
+          <t>262472; 312075</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>389919; 441466</t>
+          <t>391202; 441301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462530; 505791</t>
+          <t>461617; 505723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>254689; 302050</t>
+          <t>255453; 299292</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211891; 247962</t>
+          <t>211581; 248733</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>154124; 191882</t>
+          <t>152239; 194207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114777; 153149</t>
+          <t>114303; 149947</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59687; 95371</t>
+          <t>60518; 94214</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>210381; 248002</t>
+          <t>210640; 245750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>195068; 235346</t>
+          <t>196214; 234069</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131151; 171006</t>
+          <t>131559; 171919</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68381; 141621</t>
+          <t>67799; 142699</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>433393; 484013</t>
+          <t>432042; 482936</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359212; 418130</t>
+          <t>360095; 415225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>254971; 308955</t>
+          <t>254732; 311782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132375; 223215</t>
+          <t>142469; 221313</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125007; 152682</t>
+          <t>125129; 152811</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97694; 127331</t>
+          <t>98077; 127049</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166832; 188260</t>
+          <t>166752; 187955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154671; 168588</t>
+          <t>154245; 169487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>138873; 164302</t>
+          <t>141186; 165513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>132367; 160659</t>
+          <t>132940; 160091</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>176533; 196788</t>
+          <t>176214; 197074</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>182721; 195293</t>
+          <t>182948; 195404</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272500; 310477</t>
+          <t>272584; 310907</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>240610; 282110</t>
+          <t>236965; 279015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349722; 380303</t>
+          <t>347804; 379560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>340833; 361049</t>
+          <t>341291; 360747</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>143014; 175376</t>
+          <t>143345; 175575</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145854; 177207</t>
+          <t>143832; 178032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>176303; 205337</t>
+          <t>176116; 204291</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82714; 109675</t>
+          <t>84464; 110936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>138590; 170434</t>
+          <t>137489; 171140</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>170517; 204139</t>
+          <t>169792; 200492</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>195466; 224270</t>
+          <t>194986; 224127</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83024; 106449</t>
+          <t>83695; 106309</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>288306; 334983</t>
+          <t>290565; 337422</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322899; 370994</t>
+          <t>325294; 372086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>378620; 419586</t>
+          <t>380365; 419743</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>172429; 208047</t>
+          <t>173510; 209590</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>241006; 289152</t>
+          <t>240206; 290199</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>337930; 389351</t>
+          <t>337904; 389662</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>492539; 536752</t>
+          <t>492942; 538382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>314826; 371968</t>
+          <t>312389; 373674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>204097; 252339</t>
+          <t>202784; 253355</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>388224; 441575</t>
+          <t>390850; 444698</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>499328; 545883</t>
+          <t>499243; 546650</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>428777; 704473</t>
+          <t>429371; 681422</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>461776; 530085</t>
+          <t>460647; 530059</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>741835; 816680</t>
+          <t>744781; 815777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1006898; 1068420</t>
+          <t>1008265; 1071460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>769984; 1090108</t>
+          <t>774545; 1117058</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>515843; 564750</t>
+          <t>513094; 563268</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>644997; 686800</t>
+          <t>645840; 683643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>634913; 676066</t>
+          <t>632059; 675040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>241057; 757173</t>
+          <t>258251; 758813</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>598394; 644143</t>
+          <t>600735; 644332</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>660850; 707285</t>
+          <t>660048; 704033</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>706177; 744407</t>
+          <t>704959; 744336</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>585756; 620648</t>
+          <t>585942; 619395</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1130088; 1198456</t>
+          <t>1129976; 1197320</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1320783; 1380699</t>
+          <t>1320709; 1378253</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1350579; 1408262</t>
+          <t>1350539; 1408095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>719579; 1369057</t>
+          <t>645410; 1368088</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1935520; 2047449</t>
+          <t>1931499; 2040308</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2047014; 2164819</t>
+          <t>2049151; 2166148</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2443440; 2549433</t>
+          <t>2446255; 2549832</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1347645; 1940319</t>
+          <t>1388323; 1943104</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2009712; 2120774</t>
+          <t>2014386; 2124563</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2303002; 2419673</t>
+          <t>2300373; 2417984</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2628925; 2732085</t>
+          <t>2632941; 2732581</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1982363; 2366368</t>
+          <t>1978061; 2390665</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3977174; 4128712</t>
+          <t>3970701; 4129880</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4389377; 4546755</t>
+          <t>4388709; 4554484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5110015; 5256477</t>
+          <t>5108940; 5254090</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3491972; 4156024</t>
+          <t>3491842; 4185170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AF_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,29; 82,21</t>
+          <t>71,39; 81,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,62; 70,96</t>
+          <t>59,76; 71,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,28; 72,28</t>
+          <t>60,28; 72,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,25; 52,3</t>
+          <t>43,19; 54,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,53; 89,96</t>
+          <t>81,58; 89,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,63; 81,25</t>
+          <t>70,2; 81,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,74; 77,44</t>
+          <t>66,89; 77,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,51; 57,45</t>
+          <t>48,86; 57,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,34; 84,81</t>
+          <t>78,52; 85,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,78; 74,83</t>
+          <t>67,19; 75,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,99; 73,14</t>
+          <t>65,27; 73,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,51; 53,65</t>
+          <t>47,89; 55,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,98; 64,12</t>
+          <t>55,43; 64,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,09; 55,38</t>
+          <t>45,62; 55,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,88; 84,22</t>
+          <t>76,98; 83,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,58; 61,17</t>
+          <t>50,75; 61,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,79; 67,13</t>
+          <t>59,03; 67,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,16; 56,28</t>
+          <t>46,81; 56,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,44; 84,48</t>
+          <t>77,74; 84,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,98; 57,35</t>
+          <t>48,89; 56,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 64,31</t>
+          <t>58,24; 64,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,62; 54,48</t>
+          <t>47,73; 54,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,34; 83,22</t>
+          <t>78,21; 83,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,78; 57,8</t>
+          <t>51,35; 57,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,04; 52,41</t>
+          <t>40,9; 52,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,88; 64,17</t>
+          <t>53,38; 64,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,58; 77,23</t>
+          <t>67,67; 77,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,68; 45,3</t>
+          <t>35,02; 46,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,62; 46,55</t>
+          <t>36,12; 46,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,73; 71,49</t>
+          <t>61,18; 71,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,55; 80,91</t>
+          <t>71,27; 80,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,6; 51,92</t>
+          <t>43,61; 53,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,12; 47,7</t>
+          <t>39,77; 47,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,01; 66,57</t>
+          <t>59,17; 66,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,79; 77,55</t>
+          <t>71,14; 77,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,12; 47,01</t>
+          <t>41,08; 47,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,99; 69,35</t>
+          <t>59,0; 69,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,81; 52,06</t>
+          <t>41,29; 52,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 40,65</t>
+          <t>30,7; 40,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 30,42</t>
+          <t>19,86; 30,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 66,16</t>
+          <t>56,41; 66,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,45; 60,18</t>
+          <t>50,25; 60,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,05; 44,5</t>
+          <t>34,09; 44,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 30,24</t>
+          <t>26,46; 34,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,17; 66,14</t>
+          <t>59,26; 66,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,26; 54,49</t>
+          <t>47,08; 54,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,73; 41,28</t>
+          <t>34,02; 41,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 28,32</t>
+          <t>24,66; 31,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,55; 75,16</t>
+          <t>62,38; 74,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,13; 59,75</t>
+          <t>45,48; 59,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,35; 89,44</t>
+          <t>79,25; 89,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,63; 95,19</t>
+          <t>86,54; 94,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,31; 80,08</t>
+          <t>68,31; 80,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,54; 72,9</t>
+          <t>60,63; 72,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,62; 90,16</t>
+          <t>81,44; 90,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,84; 93,82</t>
+          <t>88,34; 94,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,49; 75,83</t>
+          <t>66,37; 75,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,83; 64,56</t>
+          <t>55,28; 65,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81,12; 88,53</t>
+          <t>81,73; 88,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,34; 93,38</t>
+          <t>88,69; 93,74</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52,93; 64,83</t>
+          <t>52,97; 65,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,7; 65,23</t>
+          <t>52,85; 65,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,93; 77,64</t>
+          <t>67,35; 77,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,39; 41,22</t>
+          <t>32,8; 42,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,43; 61,53</t>
+          <t>49,49; 61,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,32; 72,41</t>
+          <t>60,78; 72,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,39; 82,06</t>
+          <t>71,06; 81,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,56; 41,36</t>
+          <t>33,43; 42,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,93; 61,47</t>
+          <t>52,79; 61,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59,16; 67,67</t>
+          <t>58,69; 67,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70,93; 78,28</t>
+          <t>70,58; 78,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,98; 39,83</t>
+          <t>34,45; 41,51</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,06; 47,18</t>
+          <t>39,02; 46,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,48; 59,36</t>
+          <t>51,44; 59,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75,49; 82,45</t>
+          <t>75,48; 82,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,22; 60,08</t>
+          <t>50,2; 59,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,82; 39,76</t>
+          <t>32,15; 39,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,23; 65,12</t>
+          <t>56,95; 64,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,19; 80,14</t>
+          <t>73,38; 79,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,9; 80,77</t>
+          <t>49,2; 56,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,79; 42,33</t>
+          <t>36,61; 42,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55,61; 60,91</t>
+          <t>55,53; 60,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75,52; 80,25</t>
+          <t>75,49; 80,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,85; 76,22</t>
+          <t>51,17; 56,69</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>69,06; 75,82</t>
+          <t>69,28; 75,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,23; 88,1</t>
+          <t>83,1; 87,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81,56; 87,11</t>
+          <t>81,72; 87,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,91; 82,02</t>
+          <t>78,04; 84,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,67; 82,24</t>
+          <t>76,79; 82,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,23; 85,58</t>
+          <t>80,62; 85,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,46; 90,24</t>
+          <t>85,66; 90,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,9; 86,57</t>
+          <t>81,75; 86,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,03; 78,44</t>
+          <t>74,36; 78,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82,61; 86,21</t>
+          <t>82,69; 86,26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84,42; 88,02</t>
+          <t>84,47; 88,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,34; 83,39</t>
+          <t>80,71; 84,76</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,03; 62,36</t>
+          <t>58,95; 62,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,6</t>
+          <t>60,38; 63,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,4; 75,46</t>
+          <t>72,36; 75,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40,43; 56,59</t>
+          <t>54,97; 58,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,65; 62,91</t>
+          <t>59,65; 62,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,13; 68,46</t>
+          <t>65,15; 68,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,67; 77,5</t>
+          <t>74,53; 77,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54,5; 65,87</t>
+          <t>56,62; 59,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,76; 62,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63,26; 65,65</t>
+          <t>63,18; 65,65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73,99; 76,09</t>
+          <t>74,07; 76,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,44; 59,25</t>
+          <t>56,41; 58,84</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140729</t>
+          <t>155968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>151554</t>
+          <t>167779</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>292284</t>
+          <t>323747</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>196758; 223742</t>
+          <t>194313; 222757</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>170635; 203100</t>
+          <t>171029; 205170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175822; 210819</t>
+          <t>175813; 210382</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117647; 160851</t>
+          <t>136198; 173396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>212656; 234640</t>
+          <t>212804; 234193</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>196586; 226155</t>
+          <t>195399; 227817</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>189733; 220144</t>
+          <t>190168; 221160</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>136558; 165140</t>
+          <t>153043; 181584</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>417579; 452028</t>
+          <t>418519; 453092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377017; 422485</t>
+          <t>379315; 423738</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>374347; 421259</t>
+          <t>375907; 421065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>264855; 319248</t>
+          <t>301032; 347465</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287168</t>
+          <t>297078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>270874</t>
+          <t>287272</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>558041</t>
+          <t>584350</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>269548; 314333</t>
+          <t>271748; 315510</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>232531; 279412</t>
+          <t>230142; 278838</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>384826; 421599</t>
+          <t>385353; 420055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>257004; 317112</t>
+          <t>269319; 327555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>296294; 338291</t>
+          <t>297486; 339692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>246994; 294793</t>
+          <t>245178; 293317</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>403578; 440270</t>
+          <t>405170; 441016</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>251089; 293993</t>
+          <t>265988; 308613</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>578432; 639329</t>
+          <t>579063; 641863</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>489685; 560199</t>
+          <t>490819; 556733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>800405; 850278</t>
+          <t>799082; 853220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>523580; 595899</t>
+          <t>551894; 622579</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120920</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157746</t>
+          <t>163319</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>278666</t>
+          <t>286259</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>130855; 167115</t>
+          <t>130405; 167672</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171345; 207937</t>
+          <t>172967; 208286</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>213989; 244559</t>
+          <t>214297; 245062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102242; 137501</t>
+          <t>106395; 140962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119477; 156127</t>
+          <t>121165; 156868</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>209180; 242235</t>
+          <t>207301; 242714</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240011; 271391</t>
+          <t>239056; 270651</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>141934; 172967</t>
+          <t>148363; 180840</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>262472; 312075</t>
+          <t>260192; 309019</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>391202; 441301</t>
+          <t>392198; 440016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>461617; 505723</t>
+          <t>463898; 507081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>255453; 299292</t>
+          <t>264573; 306888</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>93134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>111465</t>
+          <t>126339</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>188472</t>
+          <t>219473</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211581; 248733</t>
+          <t>211620; 249254</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152239; 194207</t>
+          <t>154014; 194787</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114303; 149947</t>
+          <t>113268; 151065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60518; 94214</t>
+          <t>73164; 114161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>210640; 245750</t>
+          <t>209541; 246724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>196214; 234069</t>
+          <t>195447; 236683</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131559; 171919</t>
+          <t>131724; 172003</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67799; 142699</t>
+          <t>110523; 145702</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>432042; 482936</t>
+          <t>432683; 482488</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360095; 415225</t>
+          <t>358730; 415164</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>254732; 311782</t>
+          <t>256928; 311346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>142469; 221313</t>
+          <t>193857; 246393</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163084</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>190022</t>
+          <t>207988</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>394356</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125129; 152811</t>
+          <t>126833; 152323</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98077; 127049</t>
+          <t>96703; 125846</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166752; 187955</t>
+          <t>166555; 187168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154245; 169487</t>
+          <t>177340; 193527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>141186; 165513</t>
+          <t>141180; 166623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>132940; 160091</t>
+          <t>133147; 159791</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>176214; 197074</t>
+          <t>178010; 197945</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>182948; 195404</t>
+          <t>200383; 213976</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272584; 310907</t>
+          <t>272110; 310175</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>236965; 279015</t>
+          <t>238921; 281346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>347804; 379560</t>
+          <t>350417; 379761</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>341291; 360747</t>
+          <t>382937; 404723</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94368</t>
+          <t>100043</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>191045</t>
+          <t>201634</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>143345; 175575</t>
+          <t>143440; 176268</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>143832; 178032</t>
+          <t>144232; 177546</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>176116; 204291</t>
+          <t>177212; 204290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84464; 110936</t>
+          <t>88635; 115735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>137489; 171140</t>
+          <t>137665; 170024</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>169792; 200492</t>
+          <t>168312; 201252</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>194986; 224127</t>
+          <t>194088; 222446</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83695; 106309</t>
+          <t>88176; 112099</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>290565; 337422</t>
+          <t>289772; 335161</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>325294; 372086</t>
+          <t>322694; 368985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>380365; 419743</t>
+          <t>378492; 419495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>173510; 209590</t>
+          <t>183932; 221666</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>344416</t>
+          <t>394662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>536814</t>
+          <t>403084</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>881231</t>
+          <t>797746</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>240206; 290199</t>
+          <t>239996; 288894</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>337904; 389662</t>
+          <t>337676; 390397</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>492942; 538382</t>
+          <t>492860; 538090</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>312389; 373674</t>
+          <t>359531; 423947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>202784; 253355</t>
+          <t>204898; 254391</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>390850; 444698</t>
+          <t>388945; 440770</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>499243; 546650</t>
+          <t>500514; 544647</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>429371; 681422</t>
+          <t>376208; 428673</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>460647; 530059</t>
+          <t>458479; 531893</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>744781; 815777</t>
+          <t>743671; 814839</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1008265; 1071460</t>
+          <t>1007834; 1070924</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>774545; 1117058</t>
+          <t>757814; 839431</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>551773</t>
+          <t>645295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>603947</t>
+          <t>696338</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1155720</t>
+          <t>1341632</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>513094; 563268</t>
+          <t>514749; 564137</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>645840; 683643</t>
+          <t>644866; 682804</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>632059; 675040</t>
+          <t>633284; 674585</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>258251; 758813</t>
+          <t>619734; 668465</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>600735; 644332</t>
+          <t>601646; 644216</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>660048; 704033</t>
+          <t>663261; 705488</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>704959; 744336</t>
+          <t>706541; 745518</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>585942; 619395</t>
+          <t>676918; 714990</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1129976; 1197320</t>
+          <t>1135015; 1199348</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1320709; 1378253</t>
+          <t>1321948; 1378986</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1350539; 1408095</t>
+          <t>1351294; 1408202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>645410; 1368088</t>
+          <t>1309228; 1374950</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1931499; 2040308</t>
+          <t>1929022; 2039205</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2049151; 2166148</t>
+          <t>2056241; 2169055</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2446255; 2549832</t>
+          <t>2444893; 2550717</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1388323; 1943104</t>
+          <t>1925935; 2061694</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2014386; 2124563</t>
+          <t>2014582; 2123827</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2300373; 2417984</t>
+          <t>2301178; 2417346</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2632941; 2732581</t>
+          <t>2627909; 2732923</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1978061; 2390665</t>
+          <t>2093941; 2208051</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3970701; 4129880</t>
+          <t>3973465; 4136987</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4388709; 4554484</t>
+          <t>4383012; 4554313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5108940; 5254090</t>
+          <t>5114418; 5252865</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3491842; 4185170</t>
+          <t>4062573; 4237959</t>
         </is>
       </c>
     </row>
